--- a/grants_email_registry.xlsx
+++ b/grants_email_registry.xlsx
@@ -29,10 +29,7 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00B8860B"/>
-    </font>
+    <font/>
   </fonts>
   <fills count="4">
     <fill>
@@ -48,7 +45,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFACD"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>

--- a/grants_email_registry.xlsx
+++ b/grants_email_registry.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registry (66 emails)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Registry (68 emails)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,9 +29,13 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B8860B"/>
+    </font>
     <font/>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +45,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001C1C1C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
     <fill>
@@ -75,12 +84,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -448,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -482,1450 +494,1494 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>youpla@niaa.gov.au</t>
+          <t>inhomecare@education.gov.au</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>National Indigenous Australians Agency</t>
+          <t>Department of Education</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>GO7044</t>
+          <t>GO8449</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>arc-ncgp@arc.gov.au</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Australian Research Council</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>GO8444</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>youpla@niaa.gov.au</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>National Indigenous Australians Agency</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>GO7044</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
           <t>tertiaryaccesspayment@education.gov.au</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>GO7530</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>tcfpmo@dewr.gov.au</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>GO8443</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>support@communitygrants.gov.au</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Attorney-General's Department</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>GO8425</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>repatriation@arts.gov.au</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>GO8407</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>remoteemploymentservice@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>GO8044</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>recovery@nema.gov.au</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>National Emergency Management Agency</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>GO6558</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>rda@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>GO7854</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>pacific.sports@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>GO7539</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>ncris@education.gov.au</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>GO7531</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>ncri@industry.gov.au</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>GO7982</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>nativetitle@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>GO4966</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>nationaltaxclinics@ato.gov.au</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>GO8377</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>natalie.murphy@ato.gov.au</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>GO8242</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>mymedicare@health.gov.au</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>GO7943</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>music@arts.gov.au</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>GO7863</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>museums@arts.gov.au</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>GO6270</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>movable.heritage@arts.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>GO4916</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>mnhp@communications.gov.au</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>GO8393</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>lrcip@infrastracture.gov.au</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>GO6341</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>localinvestments@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>GO7751</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>localenvironmentalprojects@industry.gov.au</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>GO7781</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>livingorgandonation@health.gov.au</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>GO7878</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>jpo@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>GO7222</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>ivais@arts.gov.au</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>GO7237</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>ipccgrants@industry.gov.au</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>GO6268</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>ip.unmea@defence.gov.au</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Department of Defence</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>GO7153</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>industrialtransformation@arena.gov.au</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Australian Renewable Energy Agency</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>GO8104</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>inclusionsupportprogram@education.gov.au</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>GO7960</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>ila@arts.gov.au</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>GO7754</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>iasgrants@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>GO6263</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>iasamo@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>GO8044</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>humanrights@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>GO5640</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>help@nhmrc.gov.au</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>National Health and Medical Research Council (NHMRC)</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>GO8353</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>grants@arts.gov.au</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>GO6813</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>grantconnect@arena.gov.au</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Australian Renewable Energy Agency</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>GO8121</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>grant.atm@health.gov.au</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>GO8398</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>fsegovernance@ato.gov.au</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>GO7123</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>firstnationsdigitalinclusion@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>GO8430</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>finassgeneral@ag.gov.au</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Attorney-General's Department</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>GO356</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>finass@ag.gov.au</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Attorney-General's Department</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>GO8256</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>enroute@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>GO6105</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>enquiries@industry.gov.au</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>GO8317</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>ececworkforce@education.gov.au</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>GO8408</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>ececgrants@deloitte.com.au</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>GO8343</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>drivenrebate@industry.gov.au</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>GO7372</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>disaster.ready@nema.gov.au</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>National Emergency Management Agency</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>GO8440</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>culturaldiplomacy@arts.gov.au</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>GO7269</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>cpp.vet@dewr.gov.au</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>GO7718</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>connectedbeginnings@education.gov.au</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>GO6172</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>chspselection@health.gov.au</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>GO7393</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>centralaustraliaplan@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>GO8397</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>cdg@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>GO3141</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>cctvnationalassessment@education.gov.au</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>GO8381</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>ccshelpdesk@education.gov.au</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>GO7215</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>cccfr-expansion@education.gov.au</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>GO5658</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>cccf@education.gov.au</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>GO1814</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>bulkbillingpractice@health.gov.au</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>GO7944</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>buildingfundsmallscalegrant@education.gov.au</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>GO8332</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>buildingfundaccogrant@education.gov.au</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>GO8331</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>bmti@industry.gov.au</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>GO8128</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>apprenticeshipsprogops@dewr.gov.au</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>GO5667</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>ajf.australia@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>GO8383</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>ahcrarotonga@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>GO7623</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>adsb2@industry.gov.au</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>GO7036</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>aaf@asic.gov.au</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>Australian Securities and Investments Commission</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>GO4195</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>

--- a/grants_email_registry.xlsx
+++ b/grants_email_registry.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registry (68 emails)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Registry (69 emails)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -494,42 +494,42 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>crimeprevention@homeaffairs.gov.au</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Department of Home Affairs</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>GO8453</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>inhomecare@education.gov.au</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>GO8449</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>arc-ncgp@arc.gov.au</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Australian Research Council</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>GO8444</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -538,39 +538,39 @@
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>youpla@niaa.gov.au</t>
+          <t>arc-ncgp@arc.gov.au</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>National Indigenous Australians Agency</t>
+          <t>Australian Research Council</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>GO7044</t>
+          <t>GO8444</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>tertiaryaccesspayment@education.gov.au</t>
+          <t>youpla@niaa.gov.au</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Department of Education</t>
+          <t>National Indigenous Australians Agency</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>GO7530</t>
+          <t>GO7044</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -582,17 +582,17 @@
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>tcfpmo@dewr.gov.au</t>
+          <t>tertiaryaccesspayment@education.gov.au</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Department of Employment and Workplace Relations</t>
+          <t>Department of Education</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>GO8443</t>
+          <t>GO7530</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -604,17 +604,17 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>support@communitygrants.gov.au</t>
+          <t>tcfpmo@dewr.gov.au</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Attorney-General's Department</t>
+          <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>GO8425</t>
+          <t>GO8443</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -626,17 +626,17 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>repatriation@arts.gov.au</t>
+          <t>support@communitygrants.gov.au</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
+          <t>Attorney-General's Department</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>GO8407</t>
+          <t>GO8425</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -648,17 +648,17 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>remoteemploymentservice@niaa.gov.au</t>
+          <t>repatriation@arts.gov.au</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>National Indigenous Australians Agency</t>
+          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>GO8044</t>
+          <t>GO8407</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -670,17 +670,17 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>recovery@nema.gov.au</t>
+          <t>remoteemploymentservice@niaa.gov.au</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>National Emergency Management Agency</t>
+          <t>National Indigenous Australians Agency</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>GO6558</t>
+          <t>GO8044</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -692,17 +692,17 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>rda@infrastructure.gov.au</t>
+          <t>recovery@nema.gov.au</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
+          <t>National Emergency Management Agency</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>GO7854</t>
+          <t>GO6558</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -714,17 +714,17 @@
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>pacific.sports@dfat.gov.au</t>
+          <t>rda@infrastructure.gov.au</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Department of Foreign Affairs and Trade</t>
+          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>GO7539</t>
+          <t>GO7854</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -736,17 +736,17 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>ncris@education.gov.au</t>
+          <t>pacific.sports@dfat.gov.au</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Department of Education</t>
+          <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>GO7531</t>
+          <t>GO7539</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -758,17 +758,17 @@
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>ncri@industry.gov.au</t>
+          <t>ncris@education.gov.au</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Department of Health, Disability and Ageing</t>
+          <t>Department of Education</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>GO7982</t>
+          <t>GO7531</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -780,17 +780,17 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>nativetitle@niaa.gov.au</t>
+          <t>ncri@industry.gov.au</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>National Indigenous Australians Agency</t>
+          <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>GO4966</t>
+          <t>GO7982</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -802,17 +802,17 @@
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>nationaltaxclinics@ato.gov.au</t>
+          <t>nativetitle@niaa.gov.au</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Australian Taxation Office</t>
+          <t>National Indigenous Australians Agency</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>GO8377</t>
+          <t>GO4966</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -824,7 +824,7 @@
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>natalie.murphy@ato.gov.au</t>
+          <t>nationaltaxclinics@ato.gov.au</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>GO8242</t>
+          <t>GO8377</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -846,17 +846,17 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>mymedicare@health.gov.au</t>
+          <t>natalie.murphy@ato.gov.au</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Department of Health, Disability and Ageing</t>
+          <t>Australian Taxation Office</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>GO7943</t>
+          <t>GO8242</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -868,17 +868,17 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>music@arts.gov.au</t>
+          <t>mymedicare@health.gov.au</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
+          <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>GO7863</t>
+          <t>GO7943</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>museums@arts.gov.au</t>
+          <t>music@arts.gov.au</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>GO6270</t>
+          <t>GO7863</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>movable.heritage@arts.gov.au</t>
+          <t>museums@arts.gov.au</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>GO4916</t>
+          <t>GO6270</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -934,7 +934,7 @@
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>mnhp@communications.gov.au</t>
+          <t>movable.heritage@arts.gov.au</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>GO8393</t>
+          <t>GO4916</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -956,7 +956,7 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>lrcip@infrastracture.gov.au</t>
+          <t>mnhp@communications.gov.au</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>GO6341</t>
+          <t>GO8393</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -978,17 +978,17 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>localinvestments@niaa.gov.au</t>
+          <t>lrcip@infrastracture.gov.au</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>National Indigenous Australians Agency</t>
+          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>GO7751</t>
+          <t>GO6341</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1000,17 +1000,17 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>localenvironmentalprojects@industry.gov.au</t>
+          <t>localinvestments@niaa.gov.au</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Department of Climate Change, Energy, the Environment and Water</t>
+          <t>National Indigenous Australians Agency</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>GO7781</t>
+          <t>GO7751</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1022,17 +1022,17 @@
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>livingorgandonation@health.gov.au</t>
+          <t>localenvironmentalprojects@industry.gov.au</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Department of Health, Disability and Ageing</t>
+          <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>GO7878</t>
+          <t>GO7781</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1044,17 +1044,17 @@
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>jpo@dfat.gov.au</t>
+          <t>livingorgandonation@health.gov.au</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Department of Foreign Affairs and Trade</t>
+          <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>GO7222</t>
+          <t>GO7878</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1066,17 +1066,17 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>ivais@arts.gov.au</t>
+          <t>jpo@dfat.gov.au</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
+          <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>GO7237</t>
+          <t>GO7222</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -1088,17 +1088,17 @@
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>ipccgrants@industry.gov.au</t>
+          <t>ivais@arts.gov.au</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Department of Climate Change, Energy, the Environment and Water</t>
+          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>GO6268</t>
+          <t>GO7237</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -1110,17 +1110,17 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>ip.unmea@defence.gov.au</t>
+          <t>ipccgrants@industry.gov.au</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Department of Defence</t>
+          <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>GO7153</t>
+          <t>GO6268</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -1132,17 +1132,17 @@
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>industrialtransformation@arena.gov.au</t>
+          <t>ip.unmea@defence.gov.au</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Australian Renewable Energy Agency</t>
+          <t>Department of Defence</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>GO8104</t>
+          <t>GO7153</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -1154,17 +1154,17 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>inclusionsupportprogram@education.gov.au</t>
+          <t>industrialtransformation@arena.gov.au</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Department of Education</t>
+          <t>Australian Renewable Energy Agency</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>GO7960</t>
+          <t>GO8104</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -1176,17 +1176,17 @@
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>ila@arts.gov.au</t>
+          <t>inclusionsupportprogram@education.gov.au</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
+          <t>Department of Education</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>GO7754</t>
+          <t>GO7960</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -1198,17 +1198,17 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>iasgrants@niaa.gov.au</t>
+          <t>ila@arts.gov.au</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>National Indigenous Australians Agency</t>
+          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>GO6263</t>
+          <t>GO7754</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -1220,7 +1220,7 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>iasamo@niaa.gov.au</t>
+          <t>iasgrants@niaa.gov.au</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>GO8044</t>
+          <t>GO6263</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -1242,17 +1242,17 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>humanrights@dfat.gov.au</t>
+          <t>iasamo@niaa.gov.au</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Department of Foreign Affairs and Trade</t>
+          <t>National Indigenous Australians Agency</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>GO5640</t>
+          <t>GO8044</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -1264,17 +1264,17 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>help@nhmrc.gov.au</t>
+          <t>humanrights@dfat.gov.au</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>National Health and Medical Research Council (NHMRC)</t>
+          <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>GO8353</t>
+          <t>GO5640</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -1286,17 +1286,17 @@
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>grants@arts.gov.au</t>
+          <t>help@nhmrc.gov.au</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
+          <t>National Health and Medical Research Council (NHMRC)</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>GO6813</t>
+          <t>GO8353</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -1308,17 +1308,17 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>grantconnect@arena.gov.au</t>
+          <t>grants@arts.gov.au</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Australian Renewable Energy Agency</t>
+          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>GO8121</t>
+          <t>GO6813</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -1330,17 +1330,17 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>grant.atm@health.gov.au</t>
+          <t>grantconnect@arena.gov.au</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Department of Health, Disability and Ageing</t>
+          <t>Australian Renewable Energy Agency</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>GO8398</t>
+          <t>GO8121</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -1352,17 +1352,17 @@
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>fsegovernance@ato.gov.au</t>
+          <t>grant.atm@health.gov.au</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Australian Taxation Office</t>
+          <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>GO7123</t>
+          <t>GO8398</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>firstnationsdigitalinclusion@infrastructure.gov.au</t>
+          <t>fsegovernance@ato.gov.au</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
+          <t>Australian Taxation Office</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>GO8430</t>
+          <t>GO7123</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -1396,17 +1396,17 @@
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>finassgeneral@ag.gov.au</t>
+          <t>firstnationsdigitalinclusion@infrastructure.gov.au</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Attorney-General's Department</t>
+          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>GO356</t>
+          <t>GO8430</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -1418,7 +1418,7 @@
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>finass@ag.gov.au</t>
+          <t>finassgeneral@ag.gov.au</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>GO8256</t>
+          <t>GO356</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -1440,17 +1440,17 @@
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>enroute@infrastructure.gov.au</t>
+          <t>finass@ag.gov.au</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
+          <t>Attorney-General's Department</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>GO6105</t>
+          <t>GO8256</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -1462,7 +1462,7 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>enquiries@industry.gov.au</t>
+          <t>enroute@infrastructure.gov.au</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>GO8317</t>
+          <t>GO6105</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -1484,17 +1484,17 @@
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>ececworkforce@education.gov.au</t>
+          <t>enquiries@industry.gov.au</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Department of Education</t>
+          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>GO8408</t>
+          <t>GO8317</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -1506,7 +1506,7 @@
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>ececgrants@deloitte.com.au</t>
+          <t>ececworkforce@education.gov.au</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>GO8343</t>
+          <t>GO8408</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -1528,17 +1528,17 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>drivenrebate@industry.gov.au</t>
+          <t>ececgrants@deloitte.com.au</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Department of Climate Change, Energy, the Environment and Water</t>
+          <t>Department of Education</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>GO7372</t>
+          <t>GO8343</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -1550,17 +1550,17 @@
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>disaster.ready@nema.gov.au</t>
+          <t>drivenrebate@industry.gov.au</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>National Emergency Management Agency</t>
+          <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>GO8440</t>
+          <t>GO7372</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -1572,17 +1572,17 @@
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>culturaldiplomacy@arts.gov.au</t>
+          <t>disaster.ready@nema.gov.au</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
+          <t>National Emergency Management Agency</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>GO7269</t>
+          <t>GO8440</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -1594,17 +1594,17 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>cpp.vet@dewr.gov.au</t>
+          <t>culturaldiplomacy@arts.gov.au</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Department of Employment and Workplace Relations</t>
+          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>GO7718</t>
+          <t>GO7269</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -1616,17 +1616,17 @@
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>connectedbeginnings@education.gov.au</t>
+          <t>cpp.vet@dewr.gov.au</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Department of Education</t>
+          <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>GO6172</t>
+          <t>GO7718</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -1638,17 +1638,17 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>chspselection@health.gov.au</t>
+          <t>connectedbeginnings@education.gov.au</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Department of Health, Disability and Ageing</t>
+          <t>Department of Education</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>GO7393</t>
+          <t>GO6172</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -1660,17 +1660,17 @@
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>centralaustraliaplan@niaa.gov.au</t>
+          <t>chspselection@health.gov.au</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>National Indigenous Australians Agency</t>
+          <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>GO8397</t>
+          <t>GO7393</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -1682,17 +1682,17 @@
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>cdg@infrastructure.gov.au</t>
+          <t>centralaustraliaplan@niaa.gov.au</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
+          <t>National Indigenous Australians Agency</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>GO3141</t>
+          <t>GO8397</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -1704,17 +1704,17 @@
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>cctvnationalassessment@education.gov.au</t>
+          <t>cdg@infrastructure.gov.au</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Department of Education</t>
+          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>GO8381</t>
+          <t>GO3141</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -1726,7 +1726,7 @@
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>ccshelpdesk@education.gov.au</t>
+          <t>cctvnationalassessment@education.gov.au</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>GO7215</t>
+          <t>GO8381</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -1748,7 +1748,7 @@
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>cccfr-expansion@education.gov.au</t>
+          <t>ccshelpdesk@education.gov.au</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>GO5658</t>
+          <t>GO7215</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -1770,7 +1770,7 @@
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>cccf@education.gov.au</t>
+          <t>cccfr-expansion@education.gov.au</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>GO1814</t>
+          <t>GO5658</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -1792,17 +1792,17 @@
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>bulkbillingpractice@health.gov.au</t>
+          <t>cccf@education.gov.au</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Department of Health, Disability and Ageing</t>
+          <t>Department of Education</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>GO7944</t>
+          <t>GO1814</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -1814,17 +1814,17 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>buildingfundsmallscalegrant@education.gov.au</t>
+          <t>bulkbillingpractice@health.gov.au</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Department of Education</t>
+          <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>GO8332</t>
+          <t>GO7944</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -1836,7 +1836,7 @@
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>buildingfundaccogrant@education.gov.au</t>
+          <t>buildingfundsmallscalegrant@education.gov.au</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>GO8331</t>
+          <t>GO8332</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -1858,17 +1858,17 @@
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>bmti@industry.gov.au</t>
+          <t>buildingfundaccogrant@education.gov.au</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Department of Health, Disability and Ageing</t>
+          <t>Department of Education</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>GO8128</t>
+          <t>GO8331</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -1880,17 +1880,17 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>apprenticeshipsprogops@dewr.gov.au</t>
+          <t>bmti@industry.gov.au</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Department of Employment and Workplace Relations</t>
+          <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>GO5667</t>
+          <t>GO8128</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -1902,17 +1902,17 @@
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>ajf.australia@dfat.gov.au</t>
+          <t>apprenticeshipsprogops@dewr.gov.au</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Department of Foreign Affairs and Trade</t>
+          <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>GO8383</t>
+          <t>GO5667</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -1924,7 +1924,7 @@
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>ahcrarotonga@dfat.gov.au</t>
+          <t>ajf.australia@dfat.gov.au</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>GO7623</t>
+          <t>GO8383</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -1946,17 +1946,17 @@
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>adsb2@industry.gov.au</t>
+          <t>ahcrarotonga@dfat.gov.au</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
+          <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>GO7036</t>
+          <t>GO7623</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -1968,20 +1968,42 @@
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
+          <t>adsb2@industry.gov.au</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>GO7036</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
           <t>aaf@asic.gov.au</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>Australian Securities and Investments Commission</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>GO4195</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>

--- a/grants_email_registry.xlsx
+++ b/grants_email_registry.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,13 +29,9 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00B8860B"/>
-    </font>
     <font/>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,11 +41,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001C1C1C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,15 +75,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -514,1496 +502,1496 @@
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>inhomecare@education.gov.au</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>GO8449</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>arc-ncgp@arc.gov.au</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Australian Research Council</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>GO8444</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>youpla@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>GO7044</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>tertiaryaccesspayment@education.gov.au</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>GO7530</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>tcfpmo@dewr.gov.au</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>GO8443</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>support@communitygrants.gov.au</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Attorney-General's Department</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>GO8425</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>repatriation@arts.gov.au</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>GO8407</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>remoteemploymentservice@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>GO8044</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>recovery@nema.gov.au</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>National Emergency Management Agency</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>GO6558</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>rda@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>GO7854</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>pacific.sports@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>GO7539</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>ncris@education.gov.au</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>GO7531</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>ncri@industry.gov.au</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>GO7982</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>nativetitle@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>GO4966</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>nationaltaxclinics@ato.gov.au</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>GO8377</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>natalie.murphy@ato.gov.au</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>GO8242</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>mymedicare@health.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>GO7943</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>music@arts.gov.au</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>GO7863</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>museums@arts.gov.au</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>GO6270</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>movable.heritage@arts.gov.au</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>GO4916</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>mnhp@communications.gov.au</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>GO8393</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>lrcip@infrastracture.gov.au</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>GO6341</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>localinvestments@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>GO7751</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>localenvironmentalprojects@industry.gov.au</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>GO7781</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>livingorgandonation@health.gov.au</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>GO7878</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>jpo@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>GO7222</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>ivais@arts.gov.au</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>GO7237</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>ipccgrants@industry.gov.au</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>GO6268</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>ip.unmea@defence.gov.au</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Department of Defence</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>GO7153</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>industrialtransformation@arena.gov.au</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Australian Renewable Energy Agency</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>GO8104</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>inclusionsupportprogram@education.gov.au</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>GO7960</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>ila@arts.gov.au</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>GO7754</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>iasgrants@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>GO6263</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>iasamo@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>GO8044</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>humanrights@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>GO5640</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>help@nhmrc.gov.au</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>National Health and Medical Research Council (NHMRC)</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>GO8353</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>grants@arts.gov.au</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>GO6813</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>grantconnect@arena.gov.au</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Australian Renewable Energy Agency</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>GO8121</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>grant.atm@health.gov.au</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>GO8398</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>fsegovernance@ato.gov.au</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>GO7123</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>firstnationsdigitalinclusion@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>GO8430</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>finassgeneral@ag.gov.au</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Attorney-General's Department</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>GO356</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>finass@ag.gov.au</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Attorney-General's Department</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>GO8256</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>enroute@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>GO6105</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>enquiries@industry.gov.au</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>GO8317</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>ececworkforce@education.gov.au</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>GO8408</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>ececgrants@deloitte.com.au</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>GO8343</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>drivenrebate@industry.gov.au</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>GO7372</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>disaster.ready@nema.gov.au</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>National Emergency Management Agency</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>GO8440</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>culturaldiplomacy@arts.gov.au</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>GO7269</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>cpp.vet@dewr.gov.au</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>GO7718</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>connectedbeginnings@education.gov.au</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>GO6172</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>chspselection@health.gov.au</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>GO7393</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>centralaustraliaplan@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>GO8397</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>cdg@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>GO3141</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>cctvnationalassessment@education.gov.au</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>GO8381</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>ccshelpdesk@education.gov.au</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>GO7215</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>cccfr-expansion@education.gov.au</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>GO5658</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>cccf@education.gov.au</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>GO1814</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>bulkbillingpractice@health.gov.au</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>GO7944</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>buildingfundsmallscalegrant@education.gov.au</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>GO8332</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>buildingfundaccogrant@education.gov.au</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>GO8331</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>bmti@industry.gov.au</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>GO8128</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>apprenticeshipsprogops@dewr.gov.au</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>GO5667</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>ajf.australia@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>GO8383</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>ahcrarotonga@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>GO7623</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>adsb2@industry.gov.au</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>GO7036</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>aaf@asic.gov.au</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>Australian Securities and Investments Commission</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>GO4195</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>

--- a/grants_email_registry.xlsx
+++ b/grants_email_registry.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registry (69 emails)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Registry (70 emails)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,9 +29,13 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B8860B"/>
+    </font>
     <font/>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +45,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001C1C1C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
     <fill>
@@ -75,12 +84,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -448,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -482,1516 +494,1538 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>ncp.secretariat@dfat.gov.au</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Department of Foreign Affairs and Trade</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>GO8470</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>crimeprevention@homeaffairs.gov.au</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Department of Home Affairs</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>GO8453</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>inhomecare@education.gov.au</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>GO8449</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>arc-ncgp@arc.gov.au</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Australian Research Council</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>GO8444</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>youpla@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>GO7044</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>tertiaryaccesspayment@education.gov.au</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>GO7530</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>tcfpmo@dewr.gov.au</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>GO8443</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>support@communitygrants.gov.au</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Attorney-General's Department</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>GO8425</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>repatriation@arts.gov.au</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>GO8407</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>remoteemploymentservice@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>GO8044</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>recovery@nema.gov.au</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>National Emergency Management Agency</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>GO6558</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>rda@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>GO7854</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>pacific.sports@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>GO7539</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>ncris@education.gov.au</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>GO7531</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>ncri@industry.gov.au</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>GO7982</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>nativetitle@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>GO4966</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>nationaltaxclinics@ato.gov.au</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>GO8377</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>natalie.murphy@ato.gov.au</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>GO8242</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>mymedicare@health.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>GO7943</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>music@arts.gov.au</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>GO7863</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>museums@arts.gov.au</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>GO6270</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>movable.heritage@arts.gov.au</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>GO4916</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>mnhp@communications.gov.au</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>GO8393</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>lrcip@infrastracture.gov.au</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>GO6341</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>localinvestments@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>GO7751</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>localenvironmentalprojects@industry.gov.au</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>GO7781</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>livingorgandonation@health.gov.au</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>GO7878</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>jpo@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>GO7222</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>ivais@arts.gov.au</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>GO7237</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>ipccgrants@industry.gov.au</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>GO6268</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>ip.unmea@defence.gov.au</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Department of Defence</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>GO7153</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>industrialtransformation@arena.gov.au</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Australian Renewable Energy Agency</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>GO8104</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>inclusionsupportprogram@education.gov.au</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>GO7960</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>ila@arts.gov.au</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>GO7754</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>iasgrants@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>GO6263</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>iasamo@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>GO8044</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>humanrights@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>GO5640</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>help@nhmrc.gov.au</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>National Health and Medical Research Council (NHMRC)</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>GO8353</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>grants@arts.gov.au</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>GO6813</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>grantconnect@arena.gov.au</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Australian Renewable Energy Agency</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>GO8121</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>grant.atm@health.gov.au</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>GO8398</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>fsegovernance@ato.gov.au</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>GO7123</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>firstnationsdigitalinclusion@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>GO8430</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>finassgeneral@ag.gov.au</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Attorney-General's Department</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>GO356</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>finass@ag.gov.au</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Attorney-General's Department</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>GO8256</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>enroute@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>GO6105</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>enquiries@industry.gov.au</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>GO8317</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>ececworkforce@education.gov.au</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>GO8408</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>ececgrants@deloitte.com.au</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>GO8343</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>drivenrebate@industry.gov.au</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>GO7372</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>disaster.ready@nema.gov.au</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>National Emergency Management Agency</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>GO8440</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>culturaldiplomacy@arts.gov.au</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>GO7269</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>cpp.vet@dewr.gov.au</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>GO7718</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>connectedbeginnings@education.gov.au</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>GO6172</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>chspselection@health.gov.au</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>GO7393</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>centralaustraliaplan@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>GO8397</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>cdg@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>GO3141</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>cctvnationalassessment@education.gov.au</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>GO8381</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>ccshelpdesk@education.gov.au</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>GO7215</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>cccfr-expansion@education.gov.au</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>GO5658</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>cccf@education.gov.au</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>GO1814</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>bulkbillingpractice@health.gov.au</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>GO7944</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>buildingfundsmallscalegrant@education.gov.au</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>GO8332</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>buildingfundaccogrant@education.gov.au</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>GO8331</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>bmti@industry.gov.au</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>GO8128</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>apprenticeshipsprogops@dewr.gov.au</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>GO5667</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>ajf.australia@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>GO8383</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>ahcrarotonga@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>GO7623</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>adsb2@industry.gov.au</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>GO7036</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>aaf@asic.gov.au</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>Australian Securities and Investments Commission</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>GO4195</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>

--- a/grants_email_registry.xlsx
+++ b/grants_email_registry.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,13 +29,9 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00B8860B"/>
-    </font>
     <font/>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,11 +41,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001C1C1C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,15 +75,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -514,1518 +502,1518 @@
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>crimeprevention@homeaffairs.gov.au</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Department of Home Affairs</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>GO8453</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>inhomecare@education.gov.au</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>GO8449</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>arc-ncgp@arc.gov.au</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Australian Research Council</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>GO8444</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>youpla@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>GO7044</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>tertiaryaccesspayment@education.gov.au</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>GO7530</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>tcfpmo@dewr.gov.au</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>GO8443</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>support@communitygrants.gov.au</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Attorney-General's Department</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>GO8425</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>repatriation@arts.gov.au</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>GO8407</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>remoteemploymentservice@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>GO8044</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>recovery@nema.gov.au</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>National Emergency Management Agency</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>GO6558</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>rda@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>GO7854</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>pacific.sports@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>GO7539</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>ncris@education.gov.au</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>GO7531</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>ncri@industry.gov.au</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>GO7982</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>nativetitle@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>GO4966</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>nationaltaxclinics@ato.gov.au</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>GO8377</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>natalie.murphy@ato.gov.au</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>GO8242</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>mymedicare@health.gov.au</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>GO7943</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>music@arts.gov.au</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>GO7863</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>museums@arts.gov.au</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>GO6270</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>movable.heritage@arts.gov.au</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>GO4916</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>mnhp@communications.gov.au</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>GO8393</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>lrcip@infrastracture.gov.au</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>GO6341</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>localinvestments@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>GO7751</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>localenvironmentalprojects@industry.gov.au</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>GO7781</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>livingorgandonation@health.gov.au</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>GO7878</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>jpo@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>GO7222</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>ivais@arts.gov.au</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>GO7237</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>ipccgrants@industry.gov.au</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>GO6268</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>ip.unmea@defence.gov.au</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Department of Defence</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>GO7153</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>industrialtransformation@arena.gov.au</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Australian Renewable Energy Agency</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>GO8104</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>inclusionsupportprogram@education.gov.au</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>GO7960</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>ila@arts.gov.au</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>GO7754</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>iasgrants@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>GO6263</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>iasamo@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>GO8044</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>humanrights@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>GO5640</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>help@nhmrc.gov.au</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>National Health and Medical Research Council (NHMRC)</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>GO8353</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>grants@arts.gov.au</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>GO6813</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>grantconnect@arena.gov.au</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Australian Renewable Energy Agency</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>GO8121</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>grant.atm@health.gov.au</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>GO8398</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>fsegovernance@ato.gov.au</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Australian Taxation Office</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>GO7123</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>firstnationsdigitalinclusion@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>GO8430</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>finassgeneral@ag.gov.au</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Attorney-General's Department</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>GO356</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>finass@ag.gov.au</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Attorney-General's Department</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>GO8256</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>enroute@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>GO6105</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>enquiries@industry.gov.au</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>GO8317</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>ececworkforce@education.gov.au</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>GO8408</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>ececgrants@deloitte.com.au</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>GO8343</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>drivenrebate@industry.gov.au</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>GO7372</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>disaster.ready@nema.gov.au</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>National Emergency Management Agency</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>GO8440</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>culturaldiplomacy@arts.gov.au</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>GO7269</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>cpp.vet@dewr.gov.au</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>GO7718</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>connectedbeginnings@education.gov.au</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>GO6172</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>chspselection@health.gov.au</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>GO7393</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>centralaustraliaplan@niaa.gov.au</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>National Indigenous Australians Agency</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>GO8397</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>cdg@infrastructure.gov.au</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>GO3141</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>cctvnationalassessment@education.gov.au</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>GO8381</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>ccshelpdesk@education.gov.au</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>GO7215</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>cccfr-expansion@education.gov.au</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>GO5658</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>cccf@education.gov.au</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>GO1814</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>bulkbillingpractice@health.gov.au</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>GO7944</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>buildingfundsmallscalegrant@education.gov.au</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>GO8332</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>buildingfundaccogrant@education.gov.au</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Department of Education</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>GO8331</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>bmti@industry.gov.au</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Department of Health, Disability and Ageing</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>GO8128</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>apprenticeshipsprogops@dewr.gov.au</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>Department of Employment and Workplace Relations</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>GO5667</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>ajf.australia@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>GO8383</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>ahcrarotonga@dfat.gov.au</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Department of Foreign Affairs and Trade</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>GO7623</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>adsb2@industry.gov.au</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>Department of Infrastructure, Transport, Regional Development, Communications, Sport and the Arts</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>GO7036</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>aaf@asic.gov.au</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Australian Securities and Investments Commission</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>GO4195</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
